--- a/data/S1968_69_FINAL.xlsx
+++ b/data/S1968_69_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -20812,7 +20830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20969,6 +20987,40 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0015</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1968_69_0015 'Kvalifikace o ČNHL sk. A' (L25, parent=NODE_S1968_69_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0016</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1968_69_0016 'Kvalifikace o ČNHL sk. B' (L25, parent=NODE_S1968_69_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -57679,6 +57731,105 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0015</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1968_69_0015 'Kvalifikace o ČNHL sk. A' (L25, parent=NODE_S1968_69_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0016</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1968_69_0016 'Kvalifikace o ČNHL sk. B' (L25, parent=NODE_S1968_69_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1968_69_FINAL.xlsx
+++ b/data/S1968_69_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2823,6 +2823,11 @@
           <t>CLUB_S1967_68_0382</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
           <t>TR_S1968_69_00268</t>
@@ -20830,7 +20835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20991,14 +20996,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1968_69_0015</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1968_69_0015 'Kvalifikace o ČNHL sk. A' (L25, parent=NODE_S1968_69_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -21008,17 +21008,360 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1968_69_0016</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1968_69_0016 'Kvalifikace o ČNHL sk. B' (L25, parent=NODE_S1968_69_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kamenice nad Lipou' → 'Nová Včelnice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Malé Hoštice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ludgeřovice' → 'Kovona Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -27494,12 +27837,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -27578,12 +27921,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Litoměřice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -27835,12 +28178,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -28564,12 +28907,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín.</t>
+          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín. || TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -29031,12 +29374,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín.</t>
+          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín. || TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -29943,12 +30286,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -30079,12 +30422,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -30714,12 +31057,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -30840,12 +31183,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -33119,12 +33462,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou.</t>
+          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou. || TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Kaučuk Kralupy</t>
+          <t>Kralupy nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -34983,12 +35326,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -35750,12 +36093,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá. || TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Sm. Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -36455,12 +36798,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou.</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nad Lipou</t>
+          <t>Kamenice nad Lipou</t>
         </is>
       </c>
     </row>
@@ -37118,12 +37461,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -37796,12 +38139,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou.</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Kamenice nad Lipou' → 'Nová Včelnice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nad Lipou</t>
+          <t>Nová Včelnice</t>
         </is>
       </c>
     </row>
@@ -40408,12 +40751,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -42749,12 +43092,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -44071,12 +44414,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -44333,12 +44676,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Hradec Králové = Vysokoškolská TJ Hradec (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Vysokoskolsky klub (Univerzita Hradec Králové, dnes UHK). city Hradec Králové.</t>
+          <t>Hradec Králové = Vysokoškolská TJ Hradec (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Vysokoskolsky klub (Univerzita Hradec Králové, dnes UHK). city Hradec Králové. || TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Vysokoškolská TJ Hradec</t>
+          <t>Hradec</t>
         </is>
       </c>
     </row>
@@ -47589,12 +47932,12 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí.</t>
+          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí. || TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>Vranov nad Dyjí</t>
+          <t>Rudá Hvězda</t>
         </is>
       </c>
     </row>
@@ -47631,12 +47974,12 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí. || TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>Kablo Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -48728,12 +49071,12 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>Brno = TJ VŠ Zemědělská Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VŠ Zemědělská** = Vysoka skola zemedelska (dnes Mendelova univerzita - MENDELU). city Brno.</t>
+          <t>Brno = TJ VŠ Zemědělská Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VŠ Zemědělská** = Vysoka skola zemedelska (dnes Mendelova univerzita - MENDELU). city Brno. || TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>VŠ Zemědělská Brno</t>
+          <t>Brno</t>
         </is>
       </c>
     </row>
@@ -50236,12 +50579,12 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Olomouc = HC Olomouc (Wiki D42 - registr ustavy 04/2026). Vsechny olomoucke kluby. Hlavni chain HC Olomouc: Spartak Moravia Olomouc / Spartak ŽPB Olomouc -&gt; TJ Olomouc -&gt; HC Olomouc. ŽPB = Železárny a pružinárny Brnenske (závody). Moravia Olomouc = potravinářský podnik. Plus paralelni Slavia Olomouc, Sokol Olomouc, Dukla Olomouc (vojensky). city Olomouc.</t>
+          <t>Olomouc = HC Olomouc (Wiki D42 - registr ustavy 04/2026). Vsechny olomoucke kluby. Hlavni chain HC Olomouc: Spartak Moravia Olomouc / Spartak ŽPB Olomouc -&gt; TJ Olomouc -&gt; HC Olomouc. ŽPB = Železárny a pružinárny Brnenske (závody). Moravia Olomouc = potravinářský podnik. Plus paralelni Slavia Olomouc, Sokol Olomouc, Dukla Olomouc (vojensky). city Olomouc. || TBD: city 'Olomouc' → 'Malé Hoštice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -51101,12 +51444,12 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -53211,12 +53554,12 @@
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>Ludgeřovice = TJ Sokol Ludgeřovice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Ludgeřovice.</t>
+          <t>Ludgeřovice = TJ Sokol Ludgeřovice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Ludgeřovice. || TBD: city 'Ludgeřovice' → 'Kovona Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>Ludgeřovice</t>
+          <t>Kovona Karviná</t>
         </is>
       </c>
     </row>
@@ -53253,12 +53596,12 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -57737,11 +58080,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -57786,21 +58129,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S1968_69_0015</t>
+          <t>CLUB_S1968_69_0010</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1968_69_0015 'Kvalifikace o ČNHL sk. A' (L25, parent=NODE_S1968_69_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -57808,24 +58149,602 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1968_69_0016</t>
+          <t>CLUB_S1968_69_0012</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1968_69_0016 'Kvalifikace o ČNHL sk. B' (L25, parent=NODE_S1968_69_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0018</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0035</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0046</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0064</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0076</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0079</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0094</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0097</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0149</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0192</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0208</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0223</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0237</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0251</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0251</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kamenice nad Lipou' → 'Nová Včelnice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0314</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0317</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0369</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0400</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0407</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0483</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0484</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0505</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0510</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0515</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0547</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Malé Hoštice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0570</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0615</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ludgeřovice' → 'Kovona Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1968_69_0616</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1968_69_FINAL.xlsx
+++ b/data/S1968_69_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20835,7 +20835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20998,7 +20998,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -21010,7 +21010,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -21022,7 +21022,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -21034,7 +21034,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -21046,7 +21046,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -21058,7 +21058,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -21070,7 +21070,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21082,7 +21082,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -21094,7 +21094,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -21106,7 +21106,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -21118,7 +21118,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -21130,7 +21130,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -21142,7 +21142,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -21154,7 +21154,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -21166,7 +21166,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -21178,7 +21178,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -21190,7 +21190,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kamenice nad Lipou' → 'Nová Včelnice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -21202,166 +21202,10 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Malé Hoštice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ludgeřovice' → 'Kovona Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -21378,7 +21222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21437,6 +21281,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21479,6 +21328,11 @@
           <t>10 týmů, jeden stůl. Mistr: Dukla Jihlava. Sestup: Gottwaldov. Postup Motor ČB z kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21526,6 +21380,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21568,6 +21427,11 @@
           <t>3 skupiny: A (16 CZ), B (8 SM), C (8 SVK). Kvalifikace o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21610,6 +21474,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21652,6 +21521,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21694,6 +21568,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21736,6 +21615,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21778,6 +21662,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21825,6 +21714,11 @@
           <t>Od 1. 1. 1969 se pro skupinu C používá název Slovenská národní hokejová liga.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22218,6 +22112,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0016</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -22344,6 +22243,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0019</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -22386,6 +22290,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0020</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22428,6 +22337,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0021</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -22470,6 +22384,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0022</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -22596,6 +22515,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -22890,6 +22814,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0032</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -22932,6 +22861,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0033</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -22974,6 +22908,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0034</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -23021,6 +22960,11 @@
           <t>Kvalifikace o I.B třídu</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0035</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -23063,6 +23007,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0036</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -23105,6 +23054,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0037</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -23189,6 +23143,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0039</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -23231,6 +23190,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0040</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -23367,6 +23331,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0042</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -23409,6 +23378,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0043</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -23451,6 +23425,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0044</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -23493,6 +23472,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0045</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -23535,6 +23519,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0046</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -23577,6 +23566,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0047</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -23708,6 +23702,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0049</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -23750,6 +23749,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0050</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -23792,6 +23796,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0051</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -23834,6 +23843,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0052</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -23876,6 +23890,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0053</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -23960,6 +23979,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0055</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -24002,6 +24026,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0056</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -24044,6 +24073,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0057</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -24086,6 +24120,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0058</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -24128,6 +24167,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0059</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -24170,6 +24214,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0062</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -24254,6 +24303,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0064</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -24296,6 +24350,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0065</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -24338,6 +24397,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0066</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -24637,6 +24701,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0074</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -24679,6 +24748,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0075</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -24721,6 +24795,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0076</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24763,6 +24842,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0077</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24805,6 +24889,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0078</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -25057,6 +25146,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0087</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -25099,6 +25193,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0088</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -25529,6 +25628,11 @@
           <t>Paralelní krajská větev Slovenska.</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0096</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -25576,6 +25680,11 @@
           <t>Paralelní krajská větev Slovenska.</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0100</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -25621,6 +25730,11 @@
       <c r="K99" t="inlineStr">
         <is>
           <t>Paralelní krajská větev Slovenska.</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0104</t>
         </is>
       </c>
     </row>
@@ -27837,12 +27951,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -27921,12 +28035,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Litoměřice</t>
         </is>
       </c>
     </row>
@@ -28178,12 +28292,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -28907,12 +29021,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín. || TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Trenčín</t>
         </is>
       </c>
     </row>
@@ -29374,12 +29488,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín. || TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Trenčín</t>
         </is>
       </c>
     </row>
@@ -38139,12 +38253,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Kamenice nad Lipou' → 'Nová Včelnice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Nová Včelnice</t>
+          <t>Stranná u Kamenice nad Lipou</t>
         </is>
       </c>
     </row>
@@ -43092,12 +43206,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -44414,12 +44528,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -47932,12 +48046,12 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí. || TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí.</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>Rudá Hvězda</t>
+          <t>Vranov nad Dyjí</t>
         </is>
       </c>
     </row>
@@ -50579,12 +50693,12 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Olomouc = HC Olomouc (Wiki D42 - registr ustavy 04/2026). Vsechny olomoucke kluby. Hlavni chain HC Olomouc: Spartak Moravia Olomouc / Spartak ŽPB Olomouc -&gt; TJ Olomouc -&gt; HC Olomouc. ŽPB = Železárny a pružinárny Brnenske (závody). Moravia Olomouc = potravinářský podnik. Plus paralelni Slavia Olomouc, Sokol Olomouc, Dukla Olomouc (vojensky). city Olomouc. || TBD: city 'Olomouc' → 'Malé Hoštice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Olomouc = HC Olomouc (Wiki D42 - registr ustavy 04/2026). Vsechny olomoucke kluby. Hlavni chain HC Olomouc: Spartak Moravia Olomouc / Spartak ŽPB Olomouc -&gt; TJ Olomouc -&gt; HC Olomouc. ŽPB = Železárny a pružinárny Brnenske (závody). Moravia Olomouc = potravinářský podnik. Plus paralelni Slavia Olomouc, Sokol Olomouc, Dukla Olomouc (vojensky). city Olomouc.</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>Malé Hoštice</t>
+          <t>Olomouc</t>
         </is>
       </c>
     </row>
@@ -51444,12 +51558,12 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -53554,12 +53668,12 @@
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>Ludgeřovice = TJ Sokol Ludgeřovice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Ludgeřovice. || TBD: city 'Ludgeřovice' → 'Kovona Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Ludgeřovice = TJ Sokol Ludgeřovice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Ludgeřovice.</t>
         </is>
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>Kovona Karviná</t>
+          <t>Ludgeřovice</t>
         </is>
       </c>
     </row>
@@ -53596,12 +53710,12 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -58080,7 +58194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -58134,12 +58248,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0010</t>
+          <t>CLUB_S1968_69_0064</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -58154,12 +58268,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0012</t>
+          <t>CLUB_S1968_69_0076</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58174,12 +58288,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0018</t>
+          <t>CLUB_S1968_69_0079</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58194,12 +58308,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0035</t>
+          <t>CLUB_S1968_69_0094</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58214,12 +58328,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0046</t>
+          <t>CLUB_S1968_69_0097</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58234,12 +58348,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0064</t>
+          <t>CLUB_S1968_69_0149</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58254,12 +58368,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0076</t>
+          <t>CLUB_S1968_69_0192</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58274,12 +58388,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0079</t>
+          <t>CLUB_S1968_69_0208</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58294,12 +58408,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0094</t>
+          <t>CLUB_S1968_69_0223</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58314,12 +58428,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0097</t>
+          <t>CLUB_S1968_69_0237</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58334,12 +58448,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0149</t>
+          <t>CLUB_S1968_69_0251</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58354,12 +58468,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0192</t>
+          <t>CLUB_S1968_69_0314</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58374,12 +58488,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0208</t>
+          <t>CLUB_S1968_69_0317</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -58394,12 +58508,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0223</t>
+          <t>CLUB_S1968_69_0407</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58414,12 +58528,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0237</t>
+          <t>CLUB_S1968_69_0484</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58434,12 +58548,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0251</t>
+          <t>CLUB_S1968_69_0505</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -58454,12 +58568,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0251</t>
+          <t>CLUB_S1968_69_0510</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kamenice nad Lipou' → 'Nová Včelnice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58474,277 +58588,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1968_69_0314</t>
+          <t>CLUB_S1968_69_0515</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0317</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0369</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0400</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0407</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0483</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0484</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0505</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0510</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0515</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0547</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Olomouc' → 'Malé Hoštice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0570</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0615</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Ludgeřovice' → 'Kovona Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S1968_69_0616</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F32"/>
+  <autoFilter ref="A1:F19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1968_69_FINAL.xlsx
+++ b/data/S1968_69_FINAL.xlsx
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / skupina A / Slavoj Svobodné Dvory — odstoupil před zahájením</t>
+          <t>Krajský přebor / skupina A</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -20835,7 +20835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20996,21 +20996,26 @@
       </c>
     </row>
     <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[club-fate] Slavoj Svobodné Dvory — odstoupil před zahájením</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -21034,7 +21039,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -21046,7 +21051,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -21058,7 +21063,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -21070,7 +21075,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21082,7 +21087,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -21094,7 +21099,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -21106,7 +21111,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -21118,7 +21123,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -21130,7 +21135,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -21142,7 +21147,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -21154,7 +21159,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -21166,7 +21171,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -21178,7 +21183,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -21190,7 +21195,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -21202,10 +21207,22 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>

--- a/data/S1968_69_FINAL.xlsx
+++ b/data/S1968_69_FINAL.xlsx
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>

--- a/data/S1968_69_FINAL.xlsx
+++ b/data/S1968_69_FINAL.xlsx
@@ -55423,7 +55423,7 @@
         <v>75</v>
       </c>
       <c r="M4" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="M9" t="n">
         <v>36</v>
@@ -59124,7 +59124,7 @@
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
         <v>76</v>

--- a/data/S1968_69_FINAL.xlsx
+++ b/data/S1968_69_FINAL.xlsx
@@ -21239,7 +21239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21301,6 +21301,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1968_69_FINAL.xlsx
+++ b/data/S1968_69_FINAL.xlsx
@@ -21585,6 +21585,16 @@
           <t>NODE_S1968_69_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21599,6 +21609,14 @@
         <is>
           <t>NODE_S1967_68_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -21632,6 +21650,8 @@
           <t>NODE_S1968_69_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21646,6 +21666,14 @@
         <is>
           <t>NODE_S1967_68_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -21679,6 +21707,8 @@
           <t>NODE_S1968_69_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21693,6 +21723,14 @@
         <is>
           <t>NODE_S1967_68_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -21909,6 +21947,8 @@
           <t>NODE_S1968_69_0010</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21918,6 +21958,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -22532,6 +22580,8 @@
           <t>NODE_S1968_69_0023</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22546,6 +22596,14 @@
         <is>
           <t>NODE_S1967_68_0025</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -23860,6 +23918,16 @@
           <t>NODE_S1968_69_0054</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0057</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0058</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23874,6 +23942,14 @@
         <is>
           <t>NODE_S1967_68_0052</t>
         </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -23907,6 +23983,8 @@
           <t>NODE_S1968_69_0054</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23921,6 +23999,14 @@
         <is>
           <t>NODE_S1967_68_0053</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -23954,6 +24040,8 @@
           <t>NODE_S1968_69_0054</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23963,6 +24051,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>5.–7. ZČ</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -24414,6 +24510,8 @@
           <t>NODE_S1968_69_0064</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24428,6 +24526,14 @@
         <is>
           <t>NODE_S1967_68_0066</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -24906,6 +25012,8 @@
           <t>NODE_S1968_69_0075</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24920,6 +25028,14 @@
         <is>
           <t>NODE_S1967_68_0078</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81">

--- a/data/S1968_69_FINAL.xlsx
+++ b/data/S1968_69_FINAL.xlsx
@@ -719,6 +719,11 @@
           <t>Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>36</v>
       </c>
@@ -21650,8 +21655,6 @@
           <t>NODE_S1968_69_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21707,8 +21710,6 @@
           <t>NODE_S1968_69_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21947,8 +21948,6 @@
           <t>NODE_S1968_69_0010</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22580,8 +22579,6 @@
           <t>NODE_S1968_69_0023</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23983,8 +23980,6 @@
           <t>NODE_S1968_69_0054</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24040,8 +24035,6 @@
           <t>NODE_S1968_69_0054</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24510,8 +24503,6 @@
           <t>NODE_S1968_69_0064</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25012,8 +25003,6 @@
           <t>NODE_S1968_69_0075</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -58115,7 +58104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58323,6 +58312,18 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>Přímé postupy do ČNHL ze skupin JM/SM a kvalifikace o SNHL jsou vedeny odděleně od KVAL o ČNHL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>
